--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -15880,16 +15880,16 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O92" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2313871446297468</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -16028,16 +16028,16 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0009364932704658844</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18252,16 +18252,16 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -19273,6 +19273,154 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19306,7 +19454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -19399,7 +19547,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1753,9 +1747,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2297,9 +2285,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -3729,9 +3714,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4125,9 +4107,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4273,9 +4252,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4421,9 +4397,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4817,9 +4790,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -6249,9 +6219,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6645,9 +6612,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6793,9 +6757,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6941,9 +6902,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -7337,9 +7295,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8325,9 +8280,6 @@
       <c r="O47" t="n">
         <v>115</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.4223733592447758</v>
       </c>
@@ -8473,9 +8425,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.0009364932704658844</v>
       </c>
@@ -8769,9 +8718,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9165,9 +9111,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9313,9 +9256,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9461,9 +9401,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9857,9 +9794,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10845,9 +10779,6 @@
       <c r="O62" t="n">
         <v>128</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.4701199128985332</v>
       </c>
@@ -10993,9 +10924,6 @@
       <c r="O63" t="n">
         <v>7</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.003277726446630596</v>
       </c>
@@ -11289,9 +11217,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11685,9 +11610,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11833,9 +11755,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11981,9 +11900,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12377,9 +12293,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13513,9 +13426,6 @@
       <c r="O78" t="n">
         <v>114</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.4187005474252561</v>
       </c>
@@ -13809,9 +13719,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14205,9 +14112,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14353,9 +14257,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14501,9 +14402,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14897,9 +14795,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15293,9 +15188,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15441,9 +15333,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15589,9 +15478,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15737,9 +15623,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15885,9 +15768,6 @@
       <c r="O92" t="n">
         <v>63</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.2313871446297468</v>
       </c>
@@ -16033,9 +15913,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.0004682466352329422</v>
       </c>
@@ -16181,9 +16058,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16577,9 +16451,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16725,9 +16596,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -17121,9 +16989,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -17517,9 +17382,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17665,9 +17527,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17813,9 +17672,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17961,9 +17817,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18109,9 +17962,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18257,9 +18107,6 @@
       <c r="O106" t="n">
         <v>8</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.02938249455615832</v>
       </c>
@@ -18405,9 +18252,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -18801,9 +18645,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -18944,16 +18785,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19106,10 +18944,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -19343,9 +19181,6 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
@@ -19599,7 +19434,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -15763,13 +15763,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O92" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2313871446297468</v>
+        <v>0.2350599564492666</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R106" t="n">
-        <v>0.02938249455615832</v>
+        <v>0.03305530637567811</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R106" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.0367281181951979</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -15763,13 +15763,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O92" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.2424055800883061</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R106" t="n">
-        <v>0.0367281181951979</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19251,6 +19251,151 @@
         </is>
       </c>
       <c r="BC112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19289,7 +19434,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -19382,7 +19527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
@@ -19434,7 +19579,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -16014,12 +16014,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16053,95 +16053,84 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.077571156938746e-05</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16157,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16217,98 +16206,23 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -16402,17 +16316,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16451,76 +16365,165 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16555,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16591,95 +16594,81 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16695,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16755,98 +16744,23 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -16940,17 +16854,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16989,17 +16903,34 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="R99" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17007,6 +16938,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17024,7 +17013,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -17037,42 +17026,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17088,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -17148,98 +17137,23 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -17333,17 +17247,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17368,7 +17282,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -17377,81 +17291,170 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17516,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -17658,7 +17661,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -17803,7 +17806,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -17948,7 +17951,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18063,12 +18066,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18093,22 +18096,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.04040093001471769</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -18141,42 +18144,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18208,12 +18211,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18247,95 +18250,81 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18362,7 +18351,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -18411,98 +18400,23 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -18596,17 +18510,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18645,76 +18559,165 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18746,12 +18749,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18785,95 +18788,81 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18889,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -18949,98 +18938,23 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
+      <c r="R111" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG111" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN111" t="b">
-        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -19134,17 +19048,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19169,7 +19083,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19178,81 +19092,170 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19317,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -19396,6 +19399,151 @@
         </is>
       </c>
       <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19517,7 +19665,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -19527,7 +19675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -19579,7 +19727,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18250,13 +18250,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O107" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R107" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.07712904820991559</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>522</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18250,13 +18250,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O107" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R107" t="n">
-        <v>0.07712904820991559</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18250,13 +18250,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O107" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R107" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.09182029548799475</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18250,13 +18250,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O107" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R107" t="n">
-        <v>0.09182029548799475</v>
+        <v>0.09916591912703433</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19544,6 +19544,151 @@
         </is>
       </c>
       <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19582,7 +19727,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19665,7 +19810,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -19675,7 +19820,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -19727,7 +19872,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -18250,13 +18250,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O107" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R107" t="n">
-        <v>0.09916591912703433</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -26799,12 +26799,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26877,42 +26877,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26944,12 +26944,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26983,95 +26983,81 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27084,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -27147,98 +27133,23 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -27332,17 +27243,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -27381,17 +27292,34 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="R152" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -27399,6 +27327,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27416,7 +27402,7 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -27429,42 +27415,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27477,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -27540,98 +27526,23 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
+      <c r="R153" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -27725,17 +27636,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -27760,7 +27671,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -27769,81 +27680,170 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27875,12 +27875,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -27919,9 +27919,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -27930,77 +27927,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28027,7 +28015,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -28079,98 +28067,18 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -28264,17 +28172,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28299,7 +28207,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -28313,76 +28221,168 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28414,12 +28414,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -28444,7 +28444,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -28458,9 +28458,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -28469,77 +28466,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28566,7 +28554,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -28618,98 +28606,18 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -28803,17 +28711,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -28838,7 +28746,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -28852,76 +28760,168 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28953,12 +28953,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -28997,9 +28997,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -29008,77 +29005,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29093,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -29157,98 +29145,18 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -29342,17 +29250,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -29377,7 +29285,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -29391,76 +29299,168 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -29637,12 +29637,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -29681,9 +29681,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -29692,77 +29689,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29789,7 +29777,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -29841,98 +29829,18 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -30026,17 +29934,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -30061,90 +29969,182 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>26</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0.09549310730751455</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30176,12 +30176,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -30215,95 +30215,81 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>0.1028387309465541</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30316,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -30379,98 +30365,23 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -30564,17 +30475,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -30613,76 +30524,165 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30714,12 +30714,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -30753,95 +30753,81 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30854,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -30917,98 +30903,23 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -31102,17 +31013,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -31137,7 +31048,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -31146,81 +31057,170 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31252,12 +31252,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -31296,9 +31296,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31307,77 +31304,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31404,7 +31392,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -31456,98 +31444,18 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -31641,17 +31549,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -31676,7 +31584,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -31690,76 +31598,168 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="R176" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31791,12 +31791,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -31835,9 +31835,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -31846,77 +31843,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31943,7 +31931,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -31995,98 +31983,18 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -32180,17 +32088,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -32215,7 +32123,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -32229,76 +32137,168 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32330,12 +32330,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -32374,9 +32374,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -32385,77 +32382,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32470,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -32534,98 +32522,18 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -32691,6 +32599,243 @@
         </is>
       </c>
       <c r="BC181" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -32812,7 +32957,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -32822,7 +32967,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -32874,7 +33019,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -1925,17 +1925,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2151,7 +2156,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2159,17 +2164,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2310,7 +2320,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2318,17 +2328,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2544,7 +2559,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2552,17 +2567,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -5998,7 +6018,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6006,17 +6026,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6232,7 +6257,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6240,17 +6265,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6391,7 +6421,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6399,17 +6429,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6625,7 +6660,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6633,17 +6668,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10079,7 +10119,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -10087,17 +10127,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -10313,7 +10358,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -10321,17 +10366,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -10472,7 +10522,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -10480,17 +10530,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -10706,7 +10761,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -10714,17 +10769,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -14548,7 +14608,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14556,17 +14616,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -14782,7 +14847,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14790,17 +14855,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -14941,7 +15011,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -14949,17 +15019,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -15175,7 +15250,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -15183,17 +15258,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -18623,7 +18703,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18631,17 +18711,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18857,7 +18942,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -18865,17 +18950,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -19016,7 +19106,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -19024,17 +19114,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -19250,7 +19345,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19258,17 +19353,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -23095,7 +23195,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -23103,17 +23203,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -23329,7 +23434,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -23337,17 +23442,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -23488,7 +23598,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -23496,17 +23606,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -23722,7 +23837,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -23730,17 +23845,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -27158,7 +27278,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -27166,17 +27286,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -27392,7 +27517,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -27400,17 +27525,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -27551,7 +27681,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
@@ -27559,17 +27689,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS153" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -27785,7 +27920,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -27793,17 +27928,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -30215,13 +30355,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O168" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1028387309465541</v>
+        <v>0.1065115427660739</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30928,7 +31068,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -30936,17 +31076,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -31162,7 +31307,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -31170,17 +31315,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -33019,7 +33169,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O182" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R182" t="n">
-        <v>0.139566849141752</v>
+        <v>0.1616037200588708</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16">
